--- a/results/HC/shp_opt/HC_shp_opt_events.xlsx
+++ b/results/HC/shp_opt/HC_shp_opt_events.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>date_p1</t>
   </si>
@@ -58,21 +58,6 @@
     <t>2025-06-08</t>
   </si>
   <si>
-    <t>2025-07-03</t>
-  </si>
-  <si>
-    <t>2025-07-05</t>
-  </si>
-  <si>
-    <t>2025-07-06</t>
-  </si>
-  <si>
-    <t>2025-07-07</t>
-  </si>
-  <si>
-    <t>2025-07-08</t>
-  </si>
-  <si>
     <t>2025-07-23</t>
   </si>
   <si>
@@ -88,57 +73,39 @@
     <t>2025-07-28</t>
   </si>
   <si>
+    <t>2025-08-17</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
+  </si>
+  <si>
+    <t>2025-10-21</t>
+  </si>
+  <si>
+    <t>2025-10-22</t>
+  </si>
+  <si>
+    <t>2025-04-30</t>
+  </si>
+  <si>
+    <t>2025-06-06</t>
+  </si>
+  <si>
+    <t>2025-06-07</t>
+  </si>
+  <si>
+    <t>2025-06-09</t>
+  </si>
+  <si>
+    <t>2025-06-13</t>
+  </si>
+  <si>
     <t>2025-07-29</t>
   </si>
   <si>
-    <t>2025-08-07</t>
-  </si>
-  <si>
-    <t>2025-08-16</t>
-  </si>
-  <si>
-    <t>2025-08-17</t>
-  </si>
-  <si>
-    <t>2025-08-19</t>
-  </si>
-  <si>
-    <t>2025-08-20</t>
-  </si>
-  <si>
-    <t>2025-10-21</t>
-  </si>
-  <si>
-    <t>2025-10-22</t>
-  </si>
-  <si>
-    <t>2025-04-30</t>
-  </si>
-  <si>
-    <t>2025-06-06</t>
-  </si>
-  <si>
-    <t>2025-06-07</t>
-  </si>
-  <si>
-    <t>2025-06-09</t>
-  </si>
-  <si>
-    <t>2025-06-13</t>
-  </si>
-  <si>
-    <t>2025-07-10</t>
-  </si>
-  <si>
-    <t>2025-07-11</t>
-  </si>
-  <si>
-    <t>2025-07-12</t>
-  </si>
-  <si>
-    <t>2025-07-13</t>
-  </si>
-  <si>
     <t>2025-07-30</t>
   </si>
   <si>
@@ -146,15 +113,6 @@
   </si>
   <si>
     <t>2025-08-02</t>
-  </si>
-  <si>
-    <t>2025-08-03</t>
-  </si>
-  <si>
-    <t>2025-08-12</t>
-  </si>
-  <si>
-    <t>2025-08-21</t>
   </si>
   <si>
     <t>2025-08-22</t>
@@ -527,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -564,7 +522,7 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>0.32457</v>
@@ -593,7 +551,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>0.27453</v>
@@ -622,7 +580,7 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>0.26954</v>
@@ -651,7 +609,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>0.26022</v>
@@ -680,7 +638,7 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>0.23871</v>
@@ -712,25 +670,25 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>0.29055</v>
+        <v>0.3125</v>
       </c>
       <c r="D7">
-        <v>1092.19</v>
+        <v>1068.34</v>
       </c>
       <c r="E7">
-        <v>0.26109</v>
+        <v>0.25947</v>
       </c>
       <c r="F7">
-        <v>1101.82</v>
+        <v>1091.84</v>
       </c>
       <c r="G7">
-        <v>0.02946</v>
+        <v>0.05303</v>
       </c>
       <c r="H7">
-        <v>0.476379</v>
+        <v>0.341589</v>
       </c>
       <c r="I7">
-        <v>2288.004</v>
+        <v>2155.955</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -738,28 +696,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C8">
-        <v>0.27993</v>
+        <v>0.30329</v>
       </c>
       <c r="D8">
-        <v>1083.98</v>
+        <v>1079.4</v>
       </c>
       <c r="E8">
-        <v>0.24251</v>
+        <v>0.25092</v>
       </c>
       <c r="F8">
-        <v>1104.73</v>
+        <v>1100.98</v>
       </c>
       <c r="G8">
-        <v>0.03742</v>
+        <v>0.05237</v>
       </c>
       <c r="H8">
-        <v>0.294103</v>
+        <v>0.380543</v>
       </c>
       <c r="I8">
-        <v>2114.017</v>
+        <v>2202.15</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -767,28 +725,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>0.27535</v>
+        <v>0.29271</v>
       </c>
       <c r="D9">
-        <v>1073.42</v>
+        <v>1092.12</v>
       </c>
       <c r="E9">
-        <v>0.23421</v>
+        <v>0.24343</v>
       </c>
       <c r="F9">
-        <v>1121.3</v>
+        <v>1113.84</v>
       </c>
       <c r="G9">
-        <v>0.04114</v>
+        <v>0.04928</v>
       </c>
       <c r="H9">
-        <v>0.102474</v>
+        <v>0.368851</v>
       </c>
       <c r="I9">
-        <v>1832.229</v>
+        <v>2210.163</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -796,28 +754,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C10">
-        <v>0.26978</v>
+        <v>0.28111</v>
       </c>
       <c r="D10">
-        <v>1081.91</v>
+        <v>1094.1</v>
       </c>
       <c r="E10">
-        <v>0.22757</v>
+        <v>0.23753</v>
       </c>
       <c r="F10">
-        <v>1126.55</v>
+        <v>1127.76</v>
       </c>
       <c r="G10">
-        <v>0.04221</v>
+        <v>0.04358</v>
       </c>
       <c r="H10">
-        <v>0.131601</v>
+        <v>0.20188</v>
       </c>
       <c r="I10">
-        <v>1887.134</v>
+        <v>2028.769</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -825,28 +783,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C11">
-        <v>0.26109</v>
+        <v>0.25947</v>
       </c>
       <c r="D11">
-        <v>1101.82</v>
+        <v>1091.84</v>
       </c>
       <c r="E11">
-        <v>0.22254</v>
+        <v>0.22767</v>
       </c>
       <c r="F11">
-        <v>1124.91</v>
+        <v>1111.63</v>
       </c>
       <c r="G11">
-        <v>0.03854</v>
+        <v>0.0318</v>
       </c>
       <c r="H11">
-        <v>0.29444</v>
+        <v>0.277472</v>
       </c>
       <c r="I11">
-        <v>2129.339</v>
+        <v>2089.717</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -854,28 +812,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C12">
-        <v>0.3125</v>
+        <v>0.30514</v>
       </c>
       <c r="D12">
-        <v>1068.34</v>
+        <v>1085.45</v>
       </c>
       <c r="E12">
-        <v>0.25947</v>
+        <v>0.26794</v>
       </c>
       <c r="F12">
-        <v>1091.84</v>
+        <v>1101.49</v>
       </c>
       <c r="G12">
-        <v>0.05303</v>
+        <v>0.03719</v>
       </c>
       <c r="H12">
-        <v>0.341589</v>
+        <v>0.355104</v>
       </c>
       <c r="I12">
-        <v>2155.955</v>
+        <v>2195.583</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -883,28 +841,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C13">
-        <v>0.30329</v>
+        <v>0.29002</v>
       </c>
       <c r="D13">
-        <v>1079.4</v>
+        <v>1087.68</v>
       </c>
       <c r="E13">
-        <v>0.25092</v>
+        <v>0.25761</v>
       </c>
       <c r="F13">
-        <v>1100.98</v>
+        <v>1101.91</v>
       </c>
       <c r="G13">
-        <v>0.05237</v>
+        <v>0.03241</v>
       </c>
       <c r="H13">
-        <v>0.380543</v>
+        <v>0.36168</v>
       </c>
       <c r="I13">
-        <v>2202.15</v>
+        <v>2192.981</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -912,28 +870,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C14">
-        <v>0.29271</v>
+        <v>0.28262</v>
       </c>
       <c r="D14">
-        <v>1092.12</v>
+        <v>1090.86</v>
       </c>
       <c r="E14">
-        <v>0.24343</v>
+        <v>0.25211</v>
       </c>
       <c r="F14">
-        <v>1113.84</v>
+        <v>1111.47</v>
       </c>
       <c r="G14">
-        <v>0.04928</v>
+        <v>0.03051</v>
       </c>
       <c r="H14">
-        <v>0.368851</v>
+        <v>0.229128</v>
       </c>
       <c r="I14">
-        <v>2210.163</v>
+        <v>2058.661</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -941,28 +899,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C15">
-        <v>0.28111</v>
+        <v>0.32997</v>
       </c>
       <c r="D15">
-        <v>1094.1</v>
+        <v>1066.87</v>
       </c>
       <c r="E15">
-        <v>0.23753</v>
+        <v>0.31065</v>
       </c>
       <c r="F15">
-        <v>1127.76</v>
+        <v>1092.53</v>
       </c>
       <c r="G15">
-        <v>0.04358</v>
+        <v>0.01933</v>
       </c>
       <c r="H15">
-        <v>0.20188</v>
+        <v>0.005289</v>
       </c>
       <c r="I15">
-        <v>2028.769</v>
+        <v>1740.391</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -970,259 +928,27 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C16">
-        <v>0.25947</v>
+        <v>0.32589</v>
       </c>
       <c r="D16">
-        <v>1091.84</v>
+        <v>1066.89</v>
       </c>
       <c r="E16">
-        <v>0.22767</v>
+        <v>0.30808</v>
       </c>
       <c r="F16">
-        <v>1111.63</v>
+        <v>1084.17</v>
       </c>
       <c r="G16">
-        <v>0.0318</v>
+        <v>0.01781</v>
       </c>
       <c r="H16">
-        <v>0.277472</v>
+        <v>0.077191</v>
       </c>
       <c r="I16">
-        <v>2089.717</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17">
-        <v>0.25092</v>
-      </c>
-      <c r="D17">
-        <v>1100.98</v>
-      </c>
-      <c r="E17">
-        <v>0.22551</v>
-      </c>
-      <c r="F17">
-        <v>1137.74</v>
-      </c>
-      <c r="G17">
-        <v>0.02541</v>
-      </c>
-      <c r="H17">
-        <v>0.07745299999999999</v>
-      </c>
-      <c r="I17">
-        <v>1781.343</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18">
-        <v>0.31451</v>
-      </c>
-      <c r="D18">
-        <v>1062.51</v>
-      </c>
-      <c r="E18">
-        <v>0.26741</v>
-      </c>
-      <c r="F18">
-        <v>1095.23</v>
-      </c>
-      <c r="G18">
-        <v>0.0471</v>
-      </c>
-      <c r="H18">
-        <v>0.191721</v>
-      </c>
-      <c r="I18">
-        <v>1998.655</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19">
-        <v>0.31358</v>
-      </c>
-      <c r="D19">
-        <v>1074.2</v>
-      </c>
-      <c r="E19">
-        <v>0.27537</v>
-      </c>
-      <c r="F19">
-        <v>1097.26</v>
-      </c>
-      <c r="G19">
-        <v>0.03821</v>
-      </c>
-      <c r="H19">
-        <v>0.231739</v>
-      </c>
-      <c r="I19">
-        <v>2065.096</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20">
-        <v>0.30514</v>
-      </c>
-      <c r="D20">
-        <v>1085.45</v>
-      </c>
-      <c r="E20">
-        <v>0.26794</v>
-      </c>
-      <c r="F20">
-        <v>1101.49</v>
-      </c>
-      <c r="G20">
-        <v>0.03719</v>
-      </c>
-      <c r="H20">
-        <v>0.355104</v>
-      </c>
-      <c r="I20">
-        <v>2195.583</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21">
-        <v>0.29002</v>
-      </c>
-      <c r="D21">
-        <v>1087.68</v>
-      </c>
-      <c r="E21">
-        <v>0.25761</v>
-      </c>
-      <c r="F21">
-        <v>1101.91</v>
-      </c>
-      <c r="G21">
-        <v>0.03241</v>
-      </c>
-      <c r="H21">
-        <v>0.36168</v>
-      </c>
-      <c r="I21">
-        <v>2192.981</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22">
-        <v>0.28262</v>
-      </c>
-      <c r="D22">
-        <v>1090.86</v>
-      </c>
-      <c r="E22">
-        <v>0.25211</v>
-      </c>
-      <c r="F22">
-        <v>1111.47</v>
-      </c>
-      <c r="G22">
-        <v>0.03051</v>
-      </c>
-      <c r="H22">
-        <v>0.229128</v>
-      </c>
-      <c r="I22">
-        <v>2058.661</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23">
-        <v>0.32997</v>
-      </c>
-      <c r="D23">
-        <v>1066.87</v>
-      </c>
-      <c r="E23">
-        <v>0.31065</v>
-      </c>
-      <c r="F23">
-        <v>1092.53</v>
-      </c>
-      <c r="G23">
-        <v>0.01933</v>
-      </c>
-      <c r="H23">
-        <v>0.005289</v>
-      </c>
-      <c r="I23">
-        <v>1740.391</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24">
-        <v>0.32589</v>
-      </c>
-      <c r="D24">
-        <v>1066.89</v>
-      </c>
-      <c r="E24">
-        <v>0.30808</v>
-      </c>
-      <c r="F24">
-        <v>1084.17</v>
-      </c>
-      <c r="G24">
-        <v>0.01781</v>
-      </c>
-      <c r="H24">
-        <v>0.077191</v>
-      </c>
-      <c r="I24">
         <v>1863.715</v>
       </c>
     </row>
